--- a/output/pdf_financials_xlsx/FMN.xlsx
+++ b/output/pdf_financials_xlsx/FMN.xlsx
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.490571</v>
+        <v>-0.490571</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.846702</v>
+        <v>-2.846702</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.155945</v>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.490571</v>
+        <v>-0.490571</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.846702</v>
+        <v>-2.846702</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.155945</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.490571</v>
+        <v>-0.490571</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.846702</v>
+        <v>-2.846702</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.155945</v>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>56.93404</v>
+        <v>-56.93404</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>12.843833</v>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.490571</v>
+        <v>-0.490571</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.846702</v>
+        <v>-2.846702</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.155945</v>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.493315</v>
+        <v>-0.487827</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.849931</v>
+        <v>-2.843473</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.155945</v>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4848,19 +4848,19 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.520581</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.734914</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.071951</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.630963</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.408535</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -10841,7 +10841,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -11159,7 +11163,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -11722,7 +11730,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -42927,10 +42939,10 @@
         </is>
       </c>
       <c r="E452" s="5" t="n">
-        <v>0.490571</v>
+        <v>-0.490571</v>
       </c>
       <c r="F452" s="5" t="n">
-        <v>2.846702</v>
+        <v>-2.846702</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FMN.xlsx
+++ b/output/pdf_financials_xlsx/FMN.xlsx
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-6.3e-05</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.490571</v>
+        <v>-0.490508</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-2.846702</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.487827</v>
+        <v>-0.487764</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-2.843473</v>
@@ -2008,37 +2008,37 @@
         <v>0.03656</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.060335</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002996</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.02264</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.015765</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.204146</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.052827</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.116187</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.272697</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.001582</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.120177</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.002106</v>
       </c>
     </row>
     <row r="35">
@@ -2104,37 +2104,37 @@
         <v>0.03656</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.060335</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002996</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.02264</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.015765</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.204146</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.052827</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.116187</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.272697</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.001582</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.120177</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.002106</v>
       </c>
     </row>
     <row r="37">
@@ -2680,37 +2680,37 @@
         <v>0.847347</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.190401</v>
+        <v>0.130066</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.14101</v>
+        <v>0.138014</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.098994</v>
+        <v>0.07635400000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.065164</v>
+        <v>0.049399</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.22658</v>
+        <v>0.022434</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.298884</v>
+        <v>1.246057</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.621054</v>
+        <v>0.504867</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.286066</v>
+        <v>0.013369</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.013637</v>
+        <v>0.012055</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.132177</v>
+        <v>0.012</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.010774</v>
+        <v>0.008668</v>
       </c>
     </row>
     <row r="49">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -33462,7 +33462,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -37259,7 +37259,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -41060,7 +41060,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -42850,7 +42850,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E451" s="5" t="n">

--- a/output/pdf_financials_xlsx/FMN.xlsx
+++ b/output/pdf_financials_xlsx/FMN.xlsx
@@ -685,7 +685,7 @@
         <v>0.09449399999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.475137</v>
+        <v>0.506221</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.503257</v>
@@ -5656,10 +5656,10 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.012414</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.002418</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -5883,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.798</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -19044,7 +19044,11 @@
           <t>Finance cost – accretion expense 10,11</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -19781,7 +19785,11 @@
           <t>Finance cost – accretion expense 10,12</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -21474,7 +21482,11 @@
           <t>Finance cost – accretion expense 12</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -22527,7 +22539,11 @@
           <t>Proceeds from short term investment</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -40414,7 +40430,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -40426,10 +40446,10 @@
         </is>
       </c>
       <c r="G421" s="5" t="n">
-        <v>-0.031084</v>
+        <v>0.031084</v>
       </c>
       <c r="H421" s="5" t="n">
-        <v>-0.038379</v>
+        <v>0.038379</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
